--- a/data/FS_logit.xlsx
+++ b/data/FS_logit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joanna\Documents\GitHub\MTF_Future-Selves\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885B33D4-1A67-4A0B-A695-3B0824F6FA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18581C9-53B3-43FC-A3AF-521BCD9830B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mods05" sheetId="1" r:id="rId1"/>
@@ -298,9 +298,6 @@
     <t>Men</t>
   </si>
   <si>
-    <t>Spouse</t>
-  </si>
-  <si>
     <t>Women</t>
   </si>
   <si>
@@ -323,6 +320,9 @@
   </si>
   <si>
     <t>Logistic Regression Models Predicting Transitions into Marriage and Parenthood using Categorical Base-Year Expectations</t>
+  </si>
+  <si>
+    <t>Married</t>
   </si>
 </sst>
 </file>
@@ -330,7 +330,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -381,14 +381,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -686,25 +686,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.7265625" customWidth="1"/>
-    <col min="3" max="6" width="11.7265625" customWidth="1"/>
-    <col min="7" max="7" width="5.7265625" customWidth="1"/>
+    <col min="2" max="2" width="19.77734375" customWidth="1"/>
+    <col min="3" max="6" width="11.77734375" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -727,782 +727,782 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>0.207218061475723</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="2">
         <v>0.22445709776123701</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="2">
         <v>-7.0124028993093299</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="3">
         <v>2.4339289193255702E-12</v>
       </c>
       <c r="G3">
         <v>16413</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <v>1.2907335786277201</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="2">
         <v>5.3413308810890903E-2</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="2">
         <v>4.7780361866557497</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="3">
         <v>1.7854740850659801E-6</v>
       </c>
       <c r="G4">
         <v>16413</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>0.39125064240667301</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="2">
         <v>0.90129389443837804</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="2">
         <v>-1.0411774682883901</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="3">
         <v>0.29780852995835</v>
       </c>
       <c r="G5">
         <v>16413</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <v>0.33503672295117198</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="2">
         <v>0.259124802278552</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="2">
         <v>-4.2200326746018</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="3">
         <v>2.4558059441583601E-5</v>
       </c>
       <c r="G6">
         <v>16413</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>1.3926679425258599</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="2">
         <v>5.7141725276650297E-2</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="2">
         <v>5.7964874002141604</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="3">
         <v>6.8961865992180903E-9</v>
       </c>
       <c r="G7">
         <v>16413</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="2">
         <v>0.48028478428125299</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="2">
         <v>0.91048714778462103</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="2">
         <v>-0.80547655418519704</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="3">
         <v>0.42055640940366901</v>
       </c>
       <c r="G8">
         <v>16413</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="2">
         <v>1.7295284549974901</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="2">
         <v>4.0227595221640801E-2</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="2">
         <v>13.6187310966968</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="3">
         <v>5.2445681374994701E-42</v>
       </c>
       <c r="G9">
         <v>16413</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="2">
         <v>0.68542179235101397</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="2">
         <v>9.5181642655211701E-2</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="2">
         <v>-3.96842147735047</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="3">
         <v>7.2658316949336196E-5</v>
       </c>
       <c r="G10">
         <v>16413</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="2">
         <v>0.40790178656975801</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="2">
         <v>9.7824387856458306E-2</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="2">
         <v>-9.1667208187703295</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="3">
         <v>5.4422701224659396E-20</v>
       </c>
       <c r="G11">
         <v>16413</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="2">
         <v>0.248032430803967</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="2">
         <v>9.9188324776801701E-2</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="2">
         <v>-14.0560471722168</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="3">
         <v>1.2840082426704899E-44</v>
       </c>
       <c r="G12">
         <v>16413</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="2">
         <v>0.111171562656774</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="2">
         <v>0.103786864912841</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="2">
         <v>-21.165305101171601</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="3">
         <v>4.07980465367543E-98</v>
       </c>
       <c r="G13">
         <v>16413</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="2">
         <v>3.23181955270447E-2</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="2">
         <v>0.168578607674152</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="2">
         <v>-20.359195782344401</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="3">
         <v>5.1213848261017504E-91</v>
       </c>
       <c r="G14">
         <v>16413</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>11</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="2">
         <v>0.89025532765125104</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="2">
         <v>4.4348494554519301E-2</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="2">
         <v>-2.62121574961856</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="3">
         <v>8.7697647238969296E-3</v>
       </c>
       <c r="G15">
         <v>16413</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="2">
         <v>0.400062036847465</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="2">
         <v>7.7887836863673496E-2</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="2">
         <v>-11.762242843957001</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="3">
         <v>8.19980741655608E-32</v>
       </c>
       <c r="G16">
         <v>16413</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>11</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="2">
         <v>0.75841786142717404</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="2">
         <v>5.8017881189876302E-2</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="2">
         <v>-4.7661302203332703</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="3">
         <v>1.8940861554812899E-6</v>
       </c>
       <c r="G17">
         <v>16413</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
       <c r="B18" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="2">
         <v>0.92062860137221203</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="2">
         <v>4.1388697535966898E-2</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="2">
         <v>-1.99809573189735</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="3">
         <v>4.5722766438466601E-2</v>
       </c>
       <c r="G18">
         <v>16413</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>11</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="2">
         <v>1.41506498208367</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="2">
         <v>4.6405081958261103E-2</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="2">
         <v>7.4814102060426002</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="3">
         <v>7.7248279807021404E-14</v>
       </c>
       <c r="G19">
         <v>16413</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="2">
         <v>5.8292601326851101E-2</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="2">
         <v>0.21567928990278701</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="2">
         <v>-13.1782708570453</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="3">
         <v>1.8568478629694101E-39</v>
       </c>
       <c r="G20">
         <v>16413</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>23</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="2">
         <v>1.61297813019881</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="2">
         <v>5.0382617984746698E-2</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="2">
         <v>9.4890313308582996</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="3">
         <v>2.6444809721532102E-21</v>
       </c>
       <c r="G21">
         <v>16413</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="2">
         <v>40.7315968162928</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="2">
         <v>0.86612687298044899</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="2">
         <v>4.2799781896307501</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="3">
         <v>1.8797172135316299E-5</v>
       </c>
       <c r="G22">
         <v>16413</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="2">
         <v>0.48699146449856801</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="2">
         <v>0.223489810371794</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="2">
         <v>-3.21942499997277</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="3">
         <v>1.28697979118732E-3</v>
       </c>
       <c r="G23">
         <v>16413</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>26</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="2">
         <v>1.2758339689193301</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="2">
         <v>4.7479810793476802E-2</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="2">
         <v>5.1306029654219696</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="3">
         <v>2.9210997854811498E-7</v>
       </c>
       <c r="G24">
         <v>16413</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>26</v>
       </c>
       <c r="B25" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="2">
         <v>0.856427778183111</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="2">
         <v>0.75562708894851505</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="2">
         <v>-0.20510816653863501</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="3">
         <v>0.83749016178137603</v>
       </c>
       <c r="G25">
         <v>16413</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>26</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="2">
         <v>1.72948508514321</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="2">
         <v>4.01809399268079E-2</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="2">
         <v>13.633920126280501</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="3">
         <v>4.2692958486569199E-42</v>
       </c>
       <c r="G26">
         <v>16413</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="2">
         <v>0.68598944332617895</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="2">
         <v>9.5086564993375103E-2</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="2">
         <v>-3.96368340930464</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="3">
         <v>7.4114903922285007E-5</v>
       </c>
       <c r="G27">
         <v>16413</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="2">
         <v>0.408718694286064</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="2">
         <v>9.7749768863763201E-2</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="2">
         <v>-9.1532507852101404</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="3">
         <v>6.1618892337045201E-20</v>
       </c>
       <c r="G28">
         <v>16413</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>26</v>
       </c>
       <c r="B29" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="2">
         <v>0.24851084042722499</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="2">
         <v>9.9069782249246896E-2</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="2">
         <v>-14.053415474807</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="3">
         <v>1.3320476657286699E-44</v>
       </c>
       <c r="G29">
         <v>16413</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>26</v>
       </c>
       <c r="B30" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="2">
         <v>0.111039448435413</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="2">
         <v>0.103557857351242</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="2">
         <v>-21.223592354191801</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="3">
         <v>1.2225703133217199E-98</v>
       </c>
       <c r="G30">
         <v>16413</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>26</v>
       </c>
       <c r="B31" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="2">
         <v>3.2349247544566001E-2</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="2">
         <v>0.16861445098090599</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="2">
         <v>-20.3491723169221</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="3">
         <v>6.2519605626446299E-91</v>
       </c>
       <c r="G31">
         <v>16413</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>26</v>
       </c>
       <c r="B32" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="2">
         <v>0.88790392455311096</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="2">
         <v>4.4291858698705798E-2</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="2">
         <v>-2.6842796488365699</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="3">
         <v>7.2759303060233298E-3</v>
       </c>
       <c r="G32">
         <v>16413</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>26</v>
       </c>
       <c r="B33" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="2">
         <v>0.39894172177088799</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="2">
         <v>7.7821072129521607E-2</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="2">
         <v>-11.8083689717784</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="3">
         <v>4.7647215172776501E-32</v>
       </c>
       <c r="G33">
         <v>16413</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>26</v>
       </c>
       <c r="B34" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="2">
         <v>0.75792141122498002</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="2">
         <v>5.7829779443808599E-2</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="2">
         <v>-4.7929558179771101</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="3">
         <v>1.6578220989725799E-6</v>
       </c>
       <c r="G34">
         <v>16413</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>26</v>
       </c>
       <c r="B35" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="2">
         <v>0.92105550469771602</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="2">
         <v>4.13423002519945E-2</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="2">
         <v>-1.9891244162636601</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="3">
         <v>4.6704058404389001E-2</v>
       </c>
       <c r="G35">
         <v>16413</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>26</v>
       </c>
       <c r="B36" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="2">
         <v>1.41687761109652</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="2">
         <v>4.6329072419730798E-2</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="2">
         <v>7.5213158160598397</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="3">
         <v>5.7029825799883095E-14</v>
       </c>
       <c r="G36">
@@ -1521,26 +1521,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="8" width="11.7265625" customWidth="1"/>
-    <col min="9" max="9" width="10.7265625" customWidth="1"/>
+    <col min="2" max="8" width="11.77734375" customWidth="1"/>
+    <col min="9" max="9" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1569,754 +1569,754 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="2">
         <v>0.33122129059260202</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>5.7141725276650297E-2</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="2">
         <v>5.7964874002141604</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="3">
         <v>6.8961865992180903E-9</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>1.3926679425258599</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="2">
         <v>1.24510953883995</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="2">
         <v>1.5577135485977001</v>
       </c>
       <c r="I3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="2">
         <v>-0.73337605042746501</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <v>0.91048714778462103</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="2">
         <v>-0.80547655418519704</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>0.42055640940366901</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>0.48028478428125299</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="2">
         <v>8.0626261289699006E-2</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="2">
         <v>2.8610215867911202</v>
       </c>
       <c r="I4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="2">
         <v>0.54784880199029296</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>4.0227595221640801E-2</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="2">
         <v>13.6187310966968</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="3">
         <v>5.2445681374994701E-42</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>1.7295284549974901</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="2">
         <v>1.5983993389717901</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="2">
         <v>1.87141511117629</v>
       </c>
       <c r="I5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="2">
         <v>-0.37772087496244</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <v>9.5181642655211701E-2</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="2">
         <v>-3.96842147735047</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="3">
         <v>7.2658316949336196E-5</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
         <v>0.68542179235101397</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="2">
         <v>0.56877127969607399</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="2">
         <v>0.82599640699283805</v>
       </c>
       <c r="I6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="2">
         <v>-0.89672885274726</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>9.7824387856458306E-2</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="2">
         <v>-9.1667208187703295</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="3">
         <v>5.4422701224659396E-20</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>0.40790178656975801</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="2">
         <v>0.33673309919275302</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="2">
         <v>0.49411200706337099</v>
       </c>
       <c r="I7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="2">
         <v>-1.39419577199589</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="2">
         <v>9.9188324776801701E-2</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="2">
         <v>-14.0560471722168</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="3">
         <v>1.2840082426704899E-44</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="2">
         <v>0.248032430803967</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="2">
         <v>0.20421030923456801</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="2">
         <v>0.30125847691586799</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="2">
         <v>-2.1966806613743599</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="2">
         <v>0.103786864912841</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="2">
         <v>-21.165305101171601</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="3">
         <v>4.07980465367543E-98</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="2">
         <v>0.111171562656774</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="2">
         <v>9.0708617386198495E-2</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="2">
         <v>0.13625074110576699</v>
       </c>
       <c r="I9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="2">
         <v>-3.43212487835308</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="2">
         <v>0.168578607674152</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="2">
         <v>-20.359195782344401</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="3">
         <v>5.1213848261017504E-91</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
         <v>3.23181955270447E-2</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="2">
         <v>2.32246991194686E-2</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="2">
         <v>4.4972197777526701E-2</v>
       </c>
       <c r="I10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="2">
         <v>-0.11624697239817899</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="2">
         <v>4.4348494554519301E-2</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="2">
         <v>-2.62121574961856</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="3">
         <v>8.7697647238969296E-3</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>0.89025532765125104</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="2">
         <v>0.81613946818845995</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="2">
         <v>0.971101851219898</v>
       </c>
       <c r="I11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="2">
         <v>-0.91613565178103296</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="2">
         <v>7.7887836863673496E-2</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="2">
         <v>-11.762242843957001</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="3">
         <v>8.19980741655608E-32</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
         <v>0.400062036847465</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="2">
         <v>0.34342181294048002</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="2">
         <v>0.46604387751654303</v>
       </c>
       <c r="I12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="2">
         <v>-0.27652077685877402</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="2">
         <v>5.8017881189876302E-2</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="2">
         <v>-4.7661302203332703</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="3">
         <v>1.8940861554812899E-6</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>0.75841786142717404</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="2">
         <v>0.67689722706902</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="2">
         <v>0.84975625476024996</v>
       </c>
       <c r="I13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="2">
         <v>-8.2698579895405799E-2</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="2">
         <v>4.1388697535966898E-2</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="2">
         <v>-1.99809573189735</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="3">
         <v>4.5722766438466601E-2</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>0.92062860137221203</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="2">
         <v>0.84889444666064195</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="2">
         <v>0.99842450966507401</v>
       </c>
       <c r="I14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="2">
         <v>0.34717545377477799</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="2">
         <v>4.6405081958261103E-2</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="2">
         <v>7.4814102060426002</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="3">
         <v>7.7248279807021404E-14</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>1.41506498208367</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="2">
         <v>1.29203887399163</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="2">
         <v>1.54980546160596</v>
       </c>
       <c r="I15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="2">
         <v>0.24360005805468599</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="2">
         <v>4.7479810793476802E-2</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="2">
         <v>5.1306029654219696</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="3">
         <v>2.9210997854811498E-7</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>1.2758339689193301</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="2">
         <v>1.1624613712551799</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="2">
         <v>1.4002635756325199</v>
       </c>
       <c r="I16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="2">
         <v>-0.154985286801156</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="2">
         <v>0.75562708894851505</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="2">
         <v>-0.20510816653863501</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="3">
         <v>0.83749016178137603</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>0.856427778183111</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="2">
         <v>0.19475471555656801</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="2">
         <v>3.7661144026606101</v>
       </c>
       <c r="I17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="2">
         <v>0.54782372556097203</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="2">
         <v>4.01809399268079E-2</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="2">
         <v>13.633920126280501</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="3">
         <v>4.2692958486569199E-42</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>1.72948508514321</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="2">
         <v>1.5985054249771999</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="2">
         <v>1.87119706508065</v>
       </c>
       <c r="I18" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="2">
         <v>-0.37689304011200803</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="2">
         <v>9.5086564993375103E-2</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="2">
         <v>-3.96368340930464</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="3">
         <v>7.4114903922285007E-5</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>0.68598944332617895</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="2">
         <v>0.56934841278337001</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="2">
         <v>0.82652643932812997</v>
       </c>
       <c r="I19" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="2">
         <v>-0.89472814860635097</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="2">
         <v>9.7749768863763201E-2</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="2">
         <v>-9.1532507852101404</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="3">
         <v>6.1618892337045201E-20</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>0.408718694286064</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="2">
         <v>0.33745682742947702</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="2">
         <v>0.49502916367521299</v>
       </c>
       <c r="I20" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="2">
         <v>-1.39226881094733</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="2">
         <v>9.9069782249246896E-2</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="2">
         <v>-14.053415474807</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="3">
         <v>1.3320476657286699E-44</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>0.24851084042722499</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="2">
         <v>0.20465173787223201</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="2">
         <v>0.30176942767230402</v>
       </c>
       <c r="I21" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="2">
         <v>-2.1978697494963102</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="2">
         <v>0.103557857351242</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="2">
         <v>-21.223592354191801</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="3">
         <v>1.2225703133217199E-98</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
         <v>0.111039448435413</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="2">
         <v>9.0641496692453596E-2</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="2">
         <v>0.136027752836822</v>
       </c>
       <c r="I22" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="2">
         <v>-3.4311645181336901</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="2">
         <v>0.16861445098090599</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="2">
         <v>-20.3491723169221</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="3">
         <v>6.2519605626446299E-91</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="2">
         <v>3.2349247544566001E-2</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="2">
         <v>2.32453807976725E-2</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="2">
         <v>4.5018570605837999E-2</v>
       </c>
       <c r="I23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="2">
         <v>-0.118891734914081</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="2">
         <v>4.4291858698705798E-2</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="2">
         <v>-2.6842796488365699</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="3">
         <v>7.2759303060233298E-3</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="2">
         <v>0.88790392455311096</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G24" s="2">
         <v>0.81407418728354497</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H24" s="2">
         <v>0.96842940305908798</v>
       </c>
       <c r="I24" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="2">
         <v>-0.91893993348477099</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="2">
         <v>7.7821072129521607E-2</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="2">
         <v>-11.8083689717784</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="3">
         <v>4.7647215172776501E-32</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="2">
         <v>0.39894172177088799</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="2">
         <v>0.342504927384713</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H25" s="2">
         <v>0.46467797875139299</v>
       </c>
       <c r="I25" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="2">
         <v>-0.27717557783753499</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="2">
         <v>5.7829779443808599E-2</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="2">
         <v>-4.7929558179771101</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="3">
         <v>1.6578220989725799E-6</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="2">
         <v>0.75792141122498002</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="2">
         <v>0.67670357988547902</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H26" s="2">
         <v>0.84888699080102403</v>
       </c>
       <c r="I26" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="2">
         <v>-8.22349788557456E-2</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="2">
         <v>4.13423002519945E-2</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="2">
         <v>-1.9891244162636601</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="3">
         <v>4.6704058404389001E-2</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="2">
         <v>0.92105550469771602</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27" s="2">
         <v>0.84936532289393596</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H27" s="2">
         <v>0.99879665424002895</v>
       </c>
       <c r="I27" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="2">
         <v>0.34845558513390401</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="2">
         <v>4.6329072419730798E-2</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="2">
         <v>7.5213158160598397</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="3">
         <v>5.7029825799883095E-14</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="2">
         <v>1.41687761109652</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G28" s="2">
         <v>1.29388665976758</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H28" s="2">
         <v>1.5515595200488399</v>
       </c>
       <c r="I28" t="s">
@@ -2335,26 +2335,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.7265625" customWidth="1"/>
-    <col min="3" max="5" width="11.7265625" customWidth="1"/>
-    <col min="6" max="6" width="7.7265625" customWidth="1"/>
-    <col min="7" max="7" width="5.7265625" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" customWidth="1"/>
+    <col min="3" max="5" width="11.77734375" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
@@ -2377,20 +2377,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>36</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>1.4682174155069201</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="2">
         <v>0.104844512398044</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="2">
         <v>3.6630340839817102</v>
       </c>
       <c r="F3" t="s">
@@ -2400,20 +2400,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>36</v>
       </c>
       <c r="B4" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <v>0.958480120794173</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="2">
         <v>0.26007993176766397</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="2">
         <v>-0.16305162930286299</v>
       </c>
       <c r="F4" t="s">
@@ -2423,20 +2423,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>36</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>0.72640436591003199</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="2">
         <v>0.221298378509729</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="2">
         <v>-1.44442288066906</v>
       </c>
       <c r="F5" t="s">
@@ -2446,20 +2446,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>36</v>
       </c>
       <c r="B6" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <v>0.70107877234302696</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="2">
         <v>0.105163570564052</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="2">
         <v>-3.3769776450903199</v>
       </c>
       <c r="F6" t="s">
@@ -2469,20 +2469,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>36</v>
       </c>
       <c r="B7" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>0.91714375806146597</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="2">
         <v>6.3954758582287594E-2</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="2">
         <v>-1.3523786339156001</v>
       </c>
       <c r="F7" t="s">
@@ -2492,20 +2492,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>36</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="2">
         <v>1.77316272229182</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="2">
         <v>5.5211076698869203E-2</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="2">
         <v>10.374092212457001</v>
       </c>
       <c r="F8" t="s">
@@ -2515,20 +2515,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>36</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="2">
         <v>0.68604603303908895</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="2">
         <v>9.41631611835472E-2</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="2">
         <v>-4.0016769319965304</v>
       </c>
       <c r="F9" t="s">
@@ -2538,20 +2538,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>36</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="2">
         <v>0.40804129603371703</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="2">
         <v>9.6986652185699906E-2</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="2">
         <v>-9.2423738084568896</v>
       </c>
       <c r="F10" t="s">
@@ -2561,20 +2561,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>36</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="2">
         <v>0.245691915251775</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="2">
         <v>9.8406166985165494E-2</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="2">
         <v>-14.264115227312599</v>
       </c>
       <c r="F11" t="s">
@@ -2584,20 +2584,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>36</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="2">
         <v>0.11029028407477801</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="2">
         <v>0.103052067235439</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="2">
         <v>-21.393451893818501</v>
       </c>
       <c r="F12" t="s">
@@ -2607,20 +2607,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>36</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="2">
         <v>3.23487834869957E-2</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="2">
         <v>0.16776198956746899</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="2">
         <v>-20.452659582294899</v>
       </c>
       <c r="F13" t="s">
@@ -2630,20 +2630,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="2">
         <v>0.88938566667268903</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="2">
         <v>4.4330141936185397E-2</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="2">
         <v>-2.64434787803817</v>
       </c>
       <c r="F14" t="s">
@@ -2653,20 +2653,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>36</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="2">
         <v>0.39671759722620498</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="2">
         <v>7.7774474398466797E-2</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="2">
         <v>-11.887326794154699</v>
       </c>
       <c r="F15" t="s">
@@ -2676,20 +2676,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
       <c r="B16" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="2">
         <v>0.76996023434630201</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="2">
         <v>5.8072041789931E-2</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="2">
         <v>-4.5015880467873899</v>
       </c>
       <c r="F16" t="s">
@@ -2699,20 +2699,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>36</v>
       </c>
       <c r="B17" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="2">
         <v>0.91592073616730896</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="2">
         <v>4.1386424549572101E-2</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="2">
         <v>-2.1220835473576298</v>
       </c>
       <c r="F17" t="s">
@@ -2722,20 +2722,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>36</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="2">
         <v>1.3979996251695701</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="2">
         <v>4.6331961643021301E-2</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="2">
         <v>7.2313444933319797</v>
       </c>
       <c r="F18" t="s">
@@ -2745,20 +2745,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>36</v>
       </c>
       <c r="B19" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="2">
         <v>0.357549851720185</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="2">
         <v>0.421326610859308</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="2">
         <v>-2.4410527478929298</v>
       </c>
       <c r="F19" t="s">
@@ -2768,20 +2768,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
       <c r="B20" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="2">
         <v>0.73575520884752399</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="2">
         <v>0.303869571308998</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="2">
         <v>-1.0098339591176999</v>
       </c>
       <c r="F20" t="s">
@@ -2791,20 +2791,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>36</v>
       </c>
       <c r="B21" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="2">
         <v>0.899407211666999</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="2">
         <v>0.14601130729870099</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="2">
         <v>-0.72610394585343097</v>
       </c>
       <c r="F21" t="s">
@@ -2814,20 +2814,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>36</v>
       </c>
       <c r="B22" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="2">
         <v>0.970382089420605</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="2">
         <v>8.6551228024225393E-2</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="2">
         <v>-0.34737090521648201</v>
       </c>
       <c r="F22" t="s">
@@ -2837,20 +2837,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>56</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="2">
         <v>0.87233546424018804</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="2">
         <v>0.103645156235965</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="2">
         <v>-1.3177771862815499</v>
       </c>
       <c r="F23" t="s">
@@ -2860,20 +2860,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>56</v>
       </c>
       <c r="B24" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="2">
         <v>1.0331277508378101</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="2">
         <v>0.23413896857347799</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="2">
         <v>0.13919448106437299</v>
       </c>
       <c r="F24" t="s">
@@ -2883,20 +2883,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
       <c r="B25" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="2">
         <v>0.47273896293283502</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="2">
         <v>0.21473707589715599</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="2">
         <v>-3.4889732716420898</v>
       </c>
       <c r="F25" t="s">
@@ -2906,20 +2906,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>56</v>
       </c>
       <c r="B26" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="2">
         <v>0.86101281443172495</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="2">
         <v>0.104696867119943</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="2">
         <v>-1.42932539994495</v>
       </c>
       <c r="F26" t="s">
@@ -2929,20 +2929,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>56</v>
       </c>
       <c r="B27" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="2">
         <v>0.815976782128919</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="2">
         <v>6.9235275895227794E-2</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="2">
         <v>-2.93736646625009</v>
       </c>
       <c r="F27" t="s">
@@ -2952,20 +2952,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>56</v>
       </c>
       <c r="B28" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="2">
         <v>2.0379982180500802</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="2">
         <v>5.7859764443206597E-2</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="2">
         <v>12.305063238494901</v>
       </c>
       <c r="F28" t="s">
@@ -2975,20 +2975,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>56</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="2">
         <v>0.77970301683410304</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="2">
         <v>9.1688545231834798E-2</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="2">
         <v>-2.71399419437485</v>
       </c>
       <c r="F29" t="s">
@@ -2998,20 +2998,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>56</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="2">
         <v>0.57398487766559603</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="2">
         <v>9.5262599821224397E-2</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="2">
         <v>-5.8275989693938</v>
       </c>
       <c r="F30" t="s">
@@ -3021,20 +3021,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>56</v>
       </c>
       <c r="B31" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="2">
         <v>0.408015209962591</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="2">
         <v>9.6259769158597006E-2</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="2">
         <v>-9.3128295838292505</v>
       </c>
       <c r="F31" t="s">
@@ -3044,20 +3044,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>56</v>
       </c>
       <c r="B32" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="2">
         <v>0.153965574737295</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="2">
         <v>0.103831183160513</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="2">
         <v>-18.019887525811502</v>
       </c>
       <c r="F32" t="s">
@@ -3067,20 +3067,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>56</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="2">
         <v>1.15761079729293E-2</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="2">
         <v>0.36854661447141202</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="2">
         <v>-12.0983663593884</v>
       </c>
       <c r="F33" t="s">
@@ -3090,20 +3090,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>56</v>
       </c>
       <c r="B34" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="2">
         <v>0.61266606497484899</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="2">
         <v>4.7623492280085798E-2</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="2">
         <v>-10.2876799530034</v>
       </c>
       <c r="F34" t="s">
@@ -3113,20 +3113,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>56</v>
       </c>
       <c r="B35" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="2">
         <v>0.93192708103772004</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="2">
         <v>7.2709150336878595E-2</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="2">
         <v>-0.96962632984516195</v>
       </c>
       <c r="F35" t="s">
@@ -3136,20 +3136,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>56</v>
       </c>
       <c r="B36" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="2">
         <v>0.84485551891277799</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="2">
         <v>6.1523767793329E-2</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="2">
         <v>-2.7402361042941199</v>
       </c>
       <c r="F36" t="s">
@@ -3159,20 +3159,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>56</v>
       </c>
       <c r="B37" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="2">
         <v>1.01756083701972</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="2">
         <v>4.3523972991236601E-2</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="2">
         <v>0.399973302839364</v>
       </c>
       <c r="F37" t="s">
@@ -3182,20 +3182,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>56</v>
       </c>
       <c r="B38" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="2">
         <v>1.0438395539410199</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="2">
         <v>4.7913331455983602E-2</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="2">
         <v>0.89548758939315198</v>
       </c>
       <c r="F38" t="s">
@@ -3205,20 +3205,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>56</v>
       </c>
       <c r="B39" t="s">
         <v>70</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="2">
         <v>0.42692961050500999</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="2">
         <v>0.32542411283631301</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="2">
         <v>-2.6154673005525102</v>
       </c>
       <c r="F39" t="s">
@@ -3228,20 +3228,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>56</v>
       </c>
       <c r="B40" t="s">
         <v>72</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="2">
         <v>1.0139760629571399</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="2">
         <v>0.26808631934424199</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="2">
         <v>5.1771751625226903E-2</v>
       </c>
       <c r="F40" t="s">
@@ -3251,20 +3251,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>56</v>
       </c>
       <c r="B41" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="2">
         <v>0.74275252464831598</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="2">
         <v>0.14435988777546899</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="2">
         <v>-2.06007617609442</v>
       </c>
       <c r="F41" t="s">
@@ -3274,20 +3274,20 @@
         <v>16413</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>56</v>
       </c>
       <c r="B42" t="s">
         <v>76</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="2">
         <v>1.0013542298169</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="2">
         <v>9.2657060718992601E-2</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="2">
         <v>1.4605618440924799E-2</v>
       </c>
       <c r="F42" t="s">
@@ -3309,31 +3309,31 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="5" width="11.7265625" customWidth="1"/>
-    <col min="6" max="6" width="5.7265625" customWidth="1"/>
-    <col min="7" max="7" width="6.7265625" customWidth="1"/>
-    <col min="8" max="10" width="11.7265625" customWidth="1"/>
-    <col min="11" max="11" width="9.7265625" customWidth="1"/>
+    <col min="2" max="5" width="11.77734375" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" customWidth="1"/>
+    <col min="7" max="7" width="6.77734375" customWidth="1"/>
+    <col min="8" max="10" width="11.77734375" customWidth="1"/>
+    <col min="11" max="11" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>79</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>90</v>
       </c>
       <c r="G3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H3">
         <v>0.58587972597402505</v>
@@ -3403,7 +3403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -3420,10 +3420,10 @@
         <v>0.78514474600833395</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G4" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H4">
         <v>0.71587926572748195</v>
@@ -3438,9 +3438,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5">
         <v>0.62124515652699996</v>
@@ -3458,7 +3458,7 @@
         <v>90</v>
       </c>
       <c r="G5" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H5">
         <v>0.58587972597402505</v>
@@ -3473,9 +3473,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B6">
         <v>0.50977899181452202</v>
@@ -3490,10 +3490,10 @@
         <v>0.66951154539688396</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G6" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H6">
         <v>0.71587926572748195</v>
@@ -3508,9 +3508,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B7">
         <v>0.55418503786140605</v>
@@ -3528,7 +3528,7 @@
         <v>90</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H7">
         <v>0.58587972597402505</v>
@@ -3543,9 +3543,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8">
         <v>0.61857439445539597</v>
@@ -3560,10 +3560,10 @@
         <v>0.71532028911992496</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H8">
         <v>0.71587926572748195</v>
@@ -3578,9 +3578,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B9">
         <v>0.54540161334109205</v>
@@ -3598,7 +3598,7 @@
         <v>90</v>
       </c>
       <c r="G9" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H9">
         <v>0.58587972597402505</v>
@@ -3613,9 +3613,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B10">
         <v>0.65675205062588304</v>
@@ -3630,10 +3630,10 @@
         <v>0.71075444277057598</v>
       </c>
       <c r="F10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H10">
         <v>0.71587926572748195</v>
@@ -3648,9 +3648,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B11">
         <v>0.61081802422472498</v>
@@ -3668,7 +3668,7 @@
         <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H11">
         <v>0.58587972597402505</v>
@@ -3683,9 +3683,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B12">
         <v>0.72976911226920405</v>
@@ -3700,10 +3700,10 @@
         <v>0.76599426003464499</v>
       </c>
       <c r="F12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G12" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H12">
         <v>0.71587926572748195</v>
@@ -3718,7 +3718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>89</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>90</v>
       </c>
       <c r="G13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H13">
         <v>0.39157448558149199</v>
@@ -3753,7 +3753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>89</v>
       </c>
@@ -3770,10 +3770,10 @@
         <v>0.65500792373163197</v>
       </c>
       <c r="F14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H14">
         <v>0.56818301689164297</v>
@@ -3788,9 +3788,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B15">
         <v>0.44482723054700102</v>
@@ -3808,7 +3808,7 @@
         <v>90</v>
       </c>
       <c r="G15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H15">
         <v>0.39157448558149199</v>
@@ -3823,9 +3823,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B16">
         <v>0.41077524892974698</v>
@@ -3840,10 +3840,10 @@
         <v>0.526448036276702</v>
       </c>
       <c r="F16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H16">
         <v>0.56818301689164297</v>
@@ -3858,9 +3858,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B17">
         <v>0.268274217778316</v>
@@ -3878,7 +3878,7 @@
         <v>90</v>
       </c>
       <c r="G17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H17">
         <v>0.39157448558149199</v>
@@ -3893,9 +3893,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B18">
         <v>0.431054819496271</v>
@@ -3910,10 +3910,10 @@
         <v>0.51668014726487899</v>
       </c>
       <c r="F18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H18">
         <v>0.56818301689164297</v>
@@ -3928,9 +3928,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B19">
         <v>0.40039245534481399</v>
@@ -3948,7 +3948,7 @@
         <v>90</v>
       </c>
       <c r="G19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H19">
         <v>0.39157448558149199</v>
@@ -3963,9 +3963,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B20">
         <v>0.50268636173958903</v>
@@ -3980,10 +3980,10 @@
         <v>0.56266459117167</v>
       </c>
       <c r="F20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H20">
         <v>0.56818301689164297</v>
@@ -3998,9 +3998,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B21">
         <v>0.38756633085853198</v>
@@ -4018,7 +4018,7 @@
         <v>90</v>
       </c>
       <c r="G21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H21">
         <v>0.39157448558149199</v>
@@ -4033,9 +4033,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B22">
         <v>0.56359562625661097</v>
@@ -4050,10 +4050,10 @@
         <v>0.60909508667685996</v>
       </c>
       <c r="F22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H22">
         <v>0.56818301689164297</v>

--- a/data/FS_logit.xlsx
+++ b/data/FS_logit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joanna\Documents\GitHub\MTF_Future-Selves\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18581C9-53B3-43FC-A3AF-521BCD9830B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8CB803-4B8B-4BB5-A559-217B1B7FE5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mods05" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,23 @@
     <sheet name="mods06" sheetId="3" r:id="rId3"/>
     <sheet name="mods06_predict" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">mods06_predict!$A$2:$I$22</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -332,7 +348,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -345,6 +361,20 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -376,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -384,11 +414,16 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -694,15 +729,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1528,17 +1563,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2334,31 +2369,31 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" style="8" customWidth="1"/>
     <col min="3" max="5" width="11.77734375" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="8" customWidth="1"/>
     <col min="7" max="7" width="5.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -2370,18 +2405,18 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>36</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="2">
@@ -2393,18 +2428,18 @@
       <c r="E3" s="2">
         <v>3.6630340839817102</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G3">
         <v>16413</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="8" t="s">
         <v>38</v>
       </c>
       <c r="C4" s="2">
@@ -2416,18 +2451,18 @@
       <c r="E4" s="2">
         <v>-0.16305162930286299</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="8" t="s">
         <v>39</v>
       </c>
       <c r="G4">
         <v>16413</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>36</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C5" s="2">
@@ -2439,18 +2474,18 @@
       <c r="E5" s="2">
         <v>-1.44442288066906</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="8" t="s">
         <v>41</v>
       </c>
       <c r="G5">
         <v>16413</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>36</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C6" s="2">
@@ -2462,18 +2497,18 @@
       <c r="E6" s="2">
         <v>-3.3769776450903199</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G6">
         <v>16413</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C7" s="2">
@@ -2485,18 +2520,18 @@
       <c r="E7" s="2">
         <v>-1.3523786339156001</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="8" t="s">
         <v>45</v>
       </c>
       <c r="G7">
         <v>16413</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>36</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="2">
@@ -2508,18 +2543,18 @@
       <c r="E8" s="2">
         <v>10.374092212457001</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G8">
         <v>16413</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>36</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="2">
@@ -2531,18 +2566,19 @@
       <c r="E9" s="2">
         <v>-4.0016769319965304</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G9">
         <v>16413</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="2">
@@ -2554,18 +2590,18 @@
       <c r="E10" s="2">
         <v>-9.2423738084568896</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G10">
         <v>16413</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>36</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="2">
@@ -2577,18 +2613,18 @@
       <c r="E11" s="2">
         <v>-14.264115227312599</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G11">
         <v>16413</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>36</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2">
@@ -2600,18 +2636,18 @@
       <c r="E12" s="2">
         <v>-21.393451893818501</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G12">
         <v>16413</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="8" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="2">
@@ -2623,18 +2659,18 @@
       <c r="E13" s="2">
         <v>-20.452659582294899</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G13">
         <v>16413</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="8" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="2">
@@ -2646,18 +2682,18 @@
       <c r="E14" s="2">
         <v>-2.64434787803817</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G14">
         <v>16413</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>36</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="8" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="2">
@@ -2669,18 +2705,18 @@
       <c r="E15" s="2">
         <v>-11.887326794154699</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G15">
         <v>16413</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="8" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="2">
@@ -2692,18 +2728,18 @@
       <c r="E16" s="2">
         <v>-4.5015880467873899</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G16">
         <v>16413</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>36</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="8" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="2">
@@ -2715,18 +2751,18 @@
       <c r="E17" s="2">
         <v>-2.1220835473576298</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G17">
         <v>16413</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>36</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C18" s="2">
@@ -2738,18 +2774,18 @@
       <c r="E18" s="2">
         <v>7.2313444933319797</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G18">
         <v>16413</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>36</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="8" t="s">
         <v>48</v>
       </c>
       <c r="C19" s="2">
@@ -2761,18 +2797,18 @@
       <c r="E19" s="2">
         <v>-2.4410527478929298</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="8" t="s">
         <v>49</v>
       </c>
       <c r="G19">
         <v>16413</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="8" t="s">
         <v>50</v>
       </c>
       <c r="C20" s="2">
@@ -2784,18 +2820,18 @@
       <c r="E20" s="2">
         <v>-1.0098339591176999</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="8" t="s">
         <v>51</v>
       </c>
       <c r="G20">
         <v>16413</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>36</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="8" t="s">
         <v>52</v>
       </c>
       <c r="C21" s="2">
@@ -2807,18 +2843,18 @@
       <c r="E21" s="2">
         <v>-0.72610394585343097</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G21">
         <v>16413</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>36</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="8" t="s">
         <v>54</v>
       </c>
       <c r="C22" s="2">
@@ -2830,18 +2866,18 @@
       <c r="E22" s="2">
         <v>-0.34737090521648201</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="8" t="s">
         <v>55</v>
       </c>
       <c r="G22">
         <v>16413</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>56</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="2">
@@ -2853,18 +2889,18 @@
       <c r="E23" s="2">
         <v>-1.3177771862815499</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="8" t="s">
         <v>57</v>
       </c>
       <c r="G23">
         <v>16413</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>56</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="8" t="s">
         <v>58</v>
       </c>
       <c r="C24" s="2">
@@ -2876,18 +2912,18 @@
       <c r="E24" s="2">
         <v>0.13919448106437299</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="8" t="s">
         <v>59</v>
       </c>
       <c r="G24">
         <v>16413</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>56</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C25" s="2">
@@ -2899,18 +2935,18 @@
       <c r="E25" s="2">
         <v>-3.4889732716420898</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G25">
         <v>16413</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>56</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="8" t="s">
         <v>61</v>
       </c>
       <c r="C26" s="2">
@@ -2922,18 +2958,18 @@
       <c r="E26" s="2">
         <v>-1.42932539994495</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="8" t="s">
         <v>62</v>
       </c>
       <c r="G26">
         <v>16413</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>56</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="8" t="s">
         <v>63</v>
       </c>
       <c r="C27" s="2">
@@ -2945,18 +2981,18 @@
       <c r="E27" s="2">
         <v>-2.93736646625009</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="8" t="s">
         <v>64</v>
       </c>
       <c r="G27">
         <v>16413</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>56</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="2">
@@ -2968,18 +3004,18 @@
       <c r="E28" s="2">
         <v>12.305063238494901</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G28">
         <v>16413</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>56</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C29" s="2">
@@ -2991,18 +3027,19 @@
       <c r="E29" s="2">
         <v>-2.71399419437485</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="8" t="s">
         <v>65</v>
       </c>
       <c r="G29">
         <v>16413</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>56</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="2">
@@ -3014,18 +3051,18 @@
       <c r="E30" s="2">
         <v>-5.8275989693938</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G30">
         <v>16413</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>56</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="2">
@@ -3037,18 +3074,18 @@
       <c r="E31" s="2">
         <v>-9.3128295838292505</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G31">
         <v>16413</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>56</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2">
@@ -3060,18 +3097,19 @@
       <c r="E32" s="2">
         <v>-18.019887525811502</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G32">
         <v>16413</v>
       </c>
+      <c r="I32" s="2"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>56</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="8" t="s">
         <v>17</v>
       </c>
       <c r="C33" s="2">
@@ -3083,7 +3121,7 @@
       <c r="E33" s="2">
         <v>-12.0983663593884</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G33">
@@ -3094,7 +3132,7 @@
       <c r="A34" t="s">
         <v>56</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="8" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="2">
@@ -3106,7 +3144,7 @@
       <c r="E34" s="2">
         <v>-10.2876799530034</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G34">
@@ -3117,7 +3155,7 @@
       <c r="A35" t="s">
         <v>56</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="8" t="s">
         <v>19</v>
       </c>
       <c r="C35" s="2">
@@ -3129,7 +3167,7 @@
       <c r="E35" s="2">
         <v>-0.96962632984516195</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="8" t="s">
         <v>66</v>
       </c>
       <c r="G35">
@@ -3140,7 +3178,7 @@
       <c r="A36" t="s">
         <v>56</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="8" t="s">
         <v>20</v>
       </c>
       <c r="C36" s="2">
@@ -3152,7 +3190,7 @@
       <c r="E36" s="2">
         <v>-2.7402361042941199</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="8" t="s">
         <v>67</v>
       </c>
       <c r="G36">
@@ -3163,7 +3201,7 @@
       <c r="A37" t="s">
         <v>56</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="8" t="s">
         <v>21</v>
       </c>
       <c r="C37" s="2">
@@ -3175,7 +3213,7 @@
       <c r="E37" s="2">
         <v>0.399973302839364</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="8" t="s">
         <v>68</v>
       </c>
       <c r="G37">
@@ -3186,7 +3224,7 @@
       <c r="A38" t="s">
         <v>56</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C38" s="2">
@@ -3198,7 +3236,7 @@
       <c r="E38" s="2">
         <v>0.89548758939315198</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="8" t="s">
         <v>69</v>
       </c>
       <c r="G38">
@@ -3209,7 +3247,7 @@
       <c r="A39" t="s">
         <v>56</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="8" t="s">
         <v>70</v>
       </c>
       <c r="C39" s="2">
@@ -3221,7 +3259,7 @@
       <c r="E39" s="2">
         <v>-2.6154673005525102</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="8" t="s">
         <v>71</v>
       </c>
       <c r="G39">
@@ -3232,7 +3270,7 @@
       <c r="A40" t="s">
         <v>56</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C40" s="2">
@@ -3244,7 +3282,7 @@
       <c r="E40" s="2">
         <v>5.1771751625226903E-2</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="8" t="s">
         <v>73</v>
       </c>
       <c r="G40">
@@ -3255,7 +3293,7 @@
       <c r="A41" t="s">
         <v>56</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="8" t="s">
         <v>74</v>
       </c>
       <c r="C41" s="2">
@@ -3267,7 +3305,7 @@
       <c r="E41" s="2">
         <v>-2.06007617609442</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="8" t="s">
         <v>75</v>
       </c>
       <c r="G41">
@@ -3278,7 +3316,7 @@
       <c r="A42" t="s">
         <v>56</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="8" t="s">
         <v>76</v>
       </c>
       <c r="C42" s="2">
@@ -3290,7 +3328,7 @@
       <c r="E42" s="2">
         <v>1.4605618440924799E-2</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="8" t="s">
         <v>77</v>
       </c>
       <c r="G42">
@@ -3302,12 +3340,13 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3319,19 +3358,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -3368,7 +3407,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -3413,10 +3452,10 @@
       <c r="C4">
         <v>9.4839450504237796E-2</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="6">
         <v>0.71587926572748195</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>0.78514474600833395</v>
       </c>
       <c r="F4" t="s">
@@ -3438,7 +3477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -3483,10 +3522,10 @@
       <c r="C6">
         <v>0.34021364519067399</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="3">
         <v>0.34802434853560998</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="6">
         <v>0.66951154539688396</v>
       </c>
       <c r="F6" t="s">
@@ -3508,7 +3547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -3553,10 +3592,10 @@
       <c r="C8">
         <v>0.22338762672457901</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="3">
         <v>0.511407422075976</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="6">
         <v>0.71532028911992496</v>
       </c>
       <c r="F8" t="s">
@@ -3578,7 +3617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>94</v>
       </c>
@@ -3623,10 +3662,10 @@
       <c r="C10">
         <v>0.127644713570923</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="3">
         <v>0.59836469869454101</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="6">
         <v>0.71075444277057598</v>
       </c>
       <c r="F10" t="s">
@@ -3648,7 +3687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>95</v>
       </c>
@@ -3693,10 +3732,10 @@
       <c r="C12">
         <v>9.8146375501173194E-2</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="3">
         <v>0.69020415208731101</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="3">
         <v>0.76599426003464499</v>
       </c>
       <c r="F12" t="s">
@@ -3718,7 +3757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>89</v>
       </c>
@@ -3763,10 +3802,10 @@
       <c r="C14">
         <v>9.3536687694454099E-2</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="6">
         <v>0.56818301689164297</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="3">
         <v>0.65500792373163197</v>
       </c>
       <c r="F14" t="s">
@@ -3788,7 +3827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -3833,10 +3872,10 @@
       <c r="C16">
         <v>0.23807477830502399</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="3">
         <v>0.304192162328145</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="6">
         <v>0.526448036276702</v>
       </c>
       <c r="F16" t="s">
@@ -3858,7 +3897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>93</v>
       </c>
@@ -3903,10 +3942,10 @@
       <c r="C18">
         <v>0.17565054840472799</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="3">
         <v>0.34936241009909202</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="6">
         <v>0.51668014726487899</v>
       </c>
       <c r="F18" t="s">
@@ -3928,7 +3967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>94</v>
       </c>
@@ -3973,10 +4012,10 @@
       <c r="C20">
         <v>0.123073643776968</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="3">
         <v>0.44263071920449099</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="6">
         <v>0.56266459117167</v>
       </c>
       <c r="F20" t="s">
@@ -3998,7 +4037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>95</v>
       </c>
@@ -4043,10 +4082,10 @@
       <c r="C22">
         <v>9.57815784364313E-2</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="3">
         <v>0.51699980438244098</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="3">
         <v>0.60909508667685996</v>
       </c>
       <c r="F22" t="s">
@@ -4069,6 +4108,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:I22" xr:uid="{00000000-0001-0000-0300-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="Women"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
